--- a/rules/CORE-000453/negative/01/data/unit-test-coreid-CG0433-negative.xlsx
+++ b/rules/CORE-000453/negative/01/data/unit-test-coreid-CG0433-negative.xlsx
@@ -873,12 +873,8 @@
       <c r="E6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
         <v>40</v>
       </c>
